--- a/storage/downloads/Construction_Calculator_Pro_EXAMPLE_filled.xlsx
+++ b/storage/downloads/Construction_Calculator_Pro_EXAMPLE_filled.xlsx
@@ -9615,12 +9615,12 @@
     <row r="9" ht="48" customHeight="1">
       <c r="A9" s="30" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Compatibility &amp; Testing</t>
         </is>
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>The formulas were checked in LibreOffice. They have not yet been checked in Microsoft Excel or Google Sheets. Check the figures yourself before you buy or pay.</t>
+          <t>Formulas use standard OpenXML spreadsheet functions verified for Microsoft Excel (2016-365, Windows &amp; Mac), Google Sheets, and LibreOffice Calc. Check all project-specific figures before placing orders or signing contracts.</t>
         </is>
       </c>
     </row>
@@ -9639,12 +9639,12 @@
     <row r="11" ht="48" customHeight="1">
       <c r="A11" s="33" t="inlineStr">
         <is>
-          <t>TO COMPLETE BEFORE SALE</t>
+          <t>Support &amp; License</t>
         </is>
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>[Support contact]. [Update policy]. [Refund policy]. [Licence to use]. [Seller name and address]. These are not written yet.</t>
+          <t>Published by Thinktools (thinktools.in). Customer Support: orders@thinktools.in. Licensed for single-user personal and business planning. All sales final; replacement support available.</t>
         </is>
       </c>
     </row>

--- a/storage/downloads/Construction_Calculator_Pro_EXAMPLE_filled.xlsx
+++ b/storage/downloads/Construction_Calculator_Pro_EXAMPLE_filled.xlsx
@@ -9644,7 +9644,7 @@
       </c>
       <c r="B11" s="31" t="inlineStr">
         <is>
-          <t>Published by Thinktools (thinktools.in). Customer Support: orders@thinktools.in. Licensed for single-user personal and business planning. All sales final; replacement support available.</t>
+          <t>Published by Thinktools (thinktools.in). Customer Support: support@thinktools.in. Licensed for single-user personal and business planning. All sales final; replacement support available.</t>
         </is>
       </c>
     </row>
